--- a/public/templates/forms/A-118-ConfigurationDriftDetectionRecords-FORM.xlsx
+++ b/public/templates/forms/A-118-ConfigurationDriftDetectionRecords-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -672,7 +675,7 @@
       <c r="O6" s="23" t="n"/>
       <c r="P6" s="23" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Date range / System</t>
@@ -738,7 +741,7 @@
       <c r="O9" s="23" t="n"/>
       <c r="P9" s="23" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>« One row per detected drift. Record the baseline value and the detected value, triage the drift, and note the remediation. »</t>
@@ -760,7 +763,7 @@
       <c r="O10" s="23" t="n"/>
       <c r="P10" s="23" t="n"/>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -1038,7 +1041,7 @@
       <c r="O23" s="23" t="n"/>
       <c r="P23" s="23" t="n"/>
     </row>
-    <row r="24" ht="29.75" customHeight="1">
+    <row r="24" ht="34.7" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>« Summarize notable findings or exceptions from the entries above. Mirror items that need tracking into the Risk / Finding Register (POA&amp;M). »</t>
@@ -1156,7 +1159,7 @@
       <c r="O28" s="23" t="n"/>
       <c r="P28" s="23" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="50.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>[Reviewed by (role)]</t>
@@ -1570,7 +1573,7 @@
       <c r="O47" s="23" t="n"/>
       <c r="P47" s="23" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="34.7" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter’s note (internal, delete before publishing): list any [BRACKETED] field that could not be resolved from project context, and any decision needing confirmation.</t>
@@ -1840,8 +1843,18 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="G12:G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Severity" prompt="Select a value" type="list">
+      <formula1>"Low,Medium,High"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="H12:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Triage Disposition" prompt="Select a value" type="list">
+      <formula1>"Authorized change,Unauthorized drift"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1904,7 +1917,7 @@
       <c r="O2" s="23" t="n"/>
       <c r="P2" s="23" t="n"/>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, findings, sign-off, retention and revision history live on the Log tab.</t>
@@ -2068,7 +2081,7 @@
       <c r="O8" s="23" t="n"/>
       <c r="P8" s="23" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>System / System Type</t>
@@ -2136,7 +2149,7 @@
       <c r="O10" s="23" t="n"/>
       <c r="P10" s="23" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Baseline (Approved) Value</t>
@@ -2238,7 +2251,7 @@
       <c r="O13" s="23" t="n"/>
       <c r="P13" s="23" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Triage Disposition</t>
@@ -2272,7 +2285,7 @@
       <c r="O14" s="23" t="n"/>
       <c r="P14" s="23" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Remediation Action &amp; Status</t>
@@ -2428,7 +2441,7 @@
       <c r="O20" s="23" t="n"/>
       <c r="P20" s="23" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="34.7" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Small (1–5, no in-house IT)</t>
@@ -2454,7 +2467,7 @@
       <c r="O21" s="23" t="n"/>
       <c r="P21" s="23" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Medium (6–25, shared county IT)</t>
@@ -2480,7 +2493,7 @@
       <c r="O22" s="23" t="n"/>
       <c r="P22" s="23" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="34.7" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Large (25+, dedicated IT/security)</t>
@@ -3184,6 +3197,6 @@
     <mergeCell ref="A19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>